--- a/game/design/characters/odnogruppniki.xlsx
+++ b/game/design/characters/odnogruppniki.xlsx
@@ -30,17 +30,17 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00999999"/>
+      <color rgb="00777777"/>
       <sz val="11"/>
     </font>
     <font>
@@ -63,7 +63,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="003B4252"/>
+        <fgColor rgb="00FFF2B3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E7D5B"/>
       </patternFill>
     </fill>
     <fill>
@@ -73,12 +78,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2B3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E7D5B"/>
+        <fgColor rgb="003B4252"/>
       </patternFill>
     </fill>
   </fills>
@@ -110,28 +110,28 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -502,31 +502,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S27"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="52" customHeight="1">
+    <row r="1" ht="48" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>№</t>
@@ -539,85 +532,50 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Внешность (рост, волосы, стиль)</t>
+          <t>Хобби, чем увлекается</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Любимая фраза</t>
+          <t>О чём с ним интересно говорить</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Харизма (0–10)</t>
+          <t>Что бесит / о чём лучше не говорить</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Живёт: общага или дом?</t>
+          <t>Чего хочет в этом семестре</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Почему пошёл на мехмат?</t>
+          <t>Привычка, фишка</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Хобби, чем увлекается</t>
+          <t>Как знакомится с героем</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>О чём с ним интересно говорить</t>
+          <t>Как относится к преподам</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Что бесит / о чём лучше не говорить</t>
+          <t>С кем обычно на перерыве</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Чего хочет в этом семестре</t>
+          <t>Может быть любовь с героем?</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Чего боится</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Привычка, фишка</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Где сидит на паре</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Как знакомится с героем</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Как относится к преподам</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>С кем обычно на перерыве</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Может быть любовь с героем?</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Реальный случай (для ивента)</t>
         </is>
@@ -634,29 +592,26 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="n"/>
+          <t>Браво Старс</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Препод Габу</t>
+        </is>
+      </c>
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>сам подходит</t>
+        </is>
+      </c>
       <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
-      <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="n"/>
-      <c r="O2" s="4" t="n"/>
-      <c r="P2" s="4" t="n"/>
-      <c r="Q2" s="4" t="n"/>
-      <c r="R2" s="4" t="n"/>
-      <c r="S2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -669,14 +624,10 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
+          <t>Липсинги</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
@@ -685,13 +636,6 @@
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
       <c r="L3" s="4" t="n"/>
-      <c r="M3" s="4" t="n"/>
-      <c r="N3" s="4" t="n"/>
-      <c r="O3" s="4" t="n"/>
-      <c r="P3" s="4" t="n"/>
-      <c r="Q3" s="4" t="n"/>
-      <c r="R3" s="4" t="n"/>
-      <c r="S3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -704,19 +648,11 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
+          <t>Игры в том числе бравл старс</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
       <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="n"/>
@@ -724,13 +660,6 @@
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
-      <c r="M4" s="4" t="n"/>
-      <c r="N4" s="4" t="n"/>
-      <c r="O4" s="4" t="n"/>
-      <c r="P4" s="4" t="n"/>
-      <c r="Q4" s="4" t="n"/>
-      <c r="R4" s="4" t="n"/>
-      <c r="S4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -743,12 +672,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>✓ есть</t>
+          <t>Собирал свою машинку</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>✓ есть</t>
+          <t>Машинах</t>
         </is>
       </c>
       <c r="E5" s="4" t="n"/>
@@ -759,13 +688,6 @@
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="n"/>
-      <c r="O5" s="4" t="n"/>
-      <c r="P5" s="4" t="n"/>
-      <c r="Q5" s="4" t="n"/>
-      <c r="R5" s="4" t="n"/>
-      <c r="S5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -776,12 +698,12 @@
           <t>Бауржан</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Творчество</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
@@ -790,13 +712,6 @@
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
-      <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n"/>
-      <c r="O6" s="4" t="n"/>
-      <c r="P6" s="4" t="n"/>
-      <c r="Q6" s="4" t="n"/>
-      <c r="R6" s="4" t="n"/>
-      <c r="S6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -808,11 +723,7 @@
         </is>
       </c>
       <c r="C7" s="4" t="n"/>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
+      <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="n"/>
@@ -821,13 +732,6 @@
       <c r="J7" s="4" t="n"/>
       <c r="K7" s="4" t="n"/>
       <c r="L7" s="4" t="n"/>
-      <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="n"/>
-      <c r="O7" s="4" t="n"/>
-      <c r="P7" s="4" t="n"/>
-      <c r="Q7" s="4" t="n"/>
-      <c r="R7" s="4" t="n"/>
-      <c r="S7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -838,12 +742,12 @@
           <t>Мирис</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Игры и одежда и Музка</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n"/>
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="4" t="n"/>
       <c r="G8" s="4" t="n"/>
@@ -852,13 +756,6 @@
       <c r="J8" s="4" t="n"/>
       <c r="K8" s="4" t="n"/>
       <c r="L8" s="4" t="n"/>
-      <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="n"/>
-      <c r="O8" s="4" t="n"/>
-      <c r="P8" s="4" t="n"/>
-      <c r="Q8" s="4" t="n"/>
-      <c r="R8" s="4" t="n"/>
-      <c r="S8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -871,14 +768,10 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
+          <t>Игры, Саморазвитие</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="n"/>
       <c r="G9" s="4" t="n"/>
@@ -887,13 +780,6 @@
       <c r="J9" s="4" t="n"/>
       <c r="K9" s="4" t="n"/>
       <c r="L9" s="4" t="n"/>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n"/>
-      <c r="O9" s="4" t="n"/>
-      <c r="P9" s="4" t="n"/>
-      <c r="Q9" s="4" t="n"/>
-      <c r="R9" s="4" t="n"/>
-      <c r="S9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -904,12 +790,12 @@
           <t>Азиза</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Танцы</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n"/>
@@ -918,13 +804,6 @@
       <c r="J10" s="4" t="n"/>
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
-      <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n"/>
-      <c r="O10" s="4" t="n"/>
-      <c r="P10" s="4" t="n"/>
-      <c r="Q10" s="4" t="n"/>
-      <c r="R10" s="4" t="n"/>
-      <c r="S10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -945,13 +824,6 @@
       <c r="J11" s="4" t="n"/>
       <c r="K11" s="4" t="n"/>
       <c r="L11" s="4" t="n"/>
-      <c r="M11" s="4" t="n"/>
-      <c r="N11" s="4" t="n"/>
-      <c r="O11" s="4" t="n"/>
-      <c r="P11" s="4" t="n"/>
-      <c r="Q11" s="4" t="n"/>
-      <c r="R11" s="4" t="n"/>
-      <c r="S11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -972,13 +844,6 @@
       <c r="J12" s="4" t="n"/>
       <c r="K12" s="4" t="n"/>
       <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n"/>
-      <c r="N12" s="4" t="n"/>
-      <c r="O12" s="4" t="n"/>
-      <c r="P12" s="4" t="n"/>
-      <c r="Q12" s="4" t="n"/>
-      <c r="R12" s="4" t="n"/>
-      <c r="S12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -989,13 +854,17 @@
           <t>Исан</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Музыка игры фильмы</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Касания</t>
+        </is>
+      </c>
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n"/>
@@ -1003,13 +872,6 @@
       <c r="J13" s="4" t="n"/>
       <c r="K13" s="4" t="n"/>
       <c r="L13" s="4" t="n"/>
-      <c r="M13" s="4" t="n"/>
-      <c r="N13" s="4" t="n"/>
-      <c r="O13" s="4" t="n"/>
-      <c r="P13" s="4" t="n"/>
-      <c r="Q13" s="4" t="n"/>
-      <c r="R13" s="4" t="n"/>
-      <c r="S13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1021,11 +883,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n"/>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
+      <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
@@ -1034,13 +892,6 @@
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="n"/>
-      <c r="O14" s="4" t="n"/>
-      <c r="P14" s="4" t="n"/>
-      <c r="Q14" s="4" t="n"/>
-      <c r="R14" s="4" t="n"/>
-      <c r="S14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1061,13 +912,6 @@
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="n"/>
       <c r="L15" s="4" t="n"/>
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
-      <c r="O15" s="4" t="n"/>
-      <c r="P15" s="4" t="n"/>
-      <c r="Q15" s="4" t="n"/>
-      <c r="R15" s="4" t="n"/>
-      <c r="S15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1078,12 +922,12 @@
           <t>Даша</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Липсинги</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n"/>
       <c r="G16" s="4" t="n"/>
@@ -1092,13 +936,6 @@
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
       <c r="L16" s="4" t="n"/>
-      <c r="M16" s="4" t="n"/>
-      <c r="N16" s="4" t="n"/>
-      <c r="O16" s="4" t="n"/>
-      <c r="P16" s="4" t="n"/>
-      <c r="Q16" s="4" t="n"/>
-      <c r="R16" s="4" t="n"/>
-      <c r="S16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1111,33 +948,26 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="n"/>
+          <t>Свой телеграм канал. И тик токи липсинги</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Шутки про женщин и лгбт</t>
+        </is>
+      </c>
       <c r="F17" s="4" t="n"/>
       <c r="G17" s="4" t="n"/>
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="n"/>
       <c r="J17" s="4" t="n"/>
-      <c r="K17" s="4" t="n"/>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>только дружба</t>
+        </is>
+      </c>
       <c r="L17" s="4" t="n"/>
-      <c r="M17" s="4" t="n"/>
-      <c r="N17" s="4" t="n"/>
-      <c r="O17" s="4" t="n"/>
-      <c r="P17" s="4" t="n"/>
-      <c r="Q17" s="4" t="n"/>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
-      <c r="S17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1148,13 +978,17 @@
           <t>Сендир</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="n"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Кодить фильмы</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>вика</t>
+        </is>
+      </c>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
       <c r="H18" s="4" t="n"/>
@@ -1162,13 +996,6 @@
       <c r="J18" s="4" t="n"/>
       <c r="K18" s="4" t="n"/>
       <c r="L18" s="4" t="n"/>
-      <c r="M18" s="4" t="n"/>
-      <c r="N18" s="4" t="n"/>
-      <c r="O18" s="4" t="n"/>
-      <c r="P18" s="4" t="n"/>
-      <c r="Q18" s="4" t="n"/>
-      <c r="R18" s="4" t="n"/>
-      <c r="S18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1179,12 +1006,12 @@
           <t>Алнар</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Загадка</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="n"/>
       <c r="G19" s="4" t="n"/>
@@ -1193,13 +1020,6 @@
       <c r="J19" s="4" t="n"/>
       <c r="K19" s="4" t="n"/>
       <c r="L19" s="4" t="n"/>
-      <c r="M19" s="4" t="n"/>
-      <c r="N19" s="4" t="n"/>
-      <c r="O19" s="4" t="n"/>
-      <c r="P19" s="4" t="n"/>
-      <c r="Q19" s="4" t="n"/>
-      <c r="R19" s="4" t="n"/>
-      <c r="S19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1210,23 +1030,28 @@
           <t>Саид</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Кодинг и игры</t>
+        </is>
+      </c>
       <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Касания</t>
+        </is>
+      </c>
       <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Моргать</t>
+        </is>
+      </c>
       <c r="H20" s="4" t="n"/>
       <c r="I20" s="4" t="n"/>
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
       <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="n"/>
-      <c r="O20" s="4" t="n"/>
-      <c r="P20" s="4" t="n"/>
-      <c r="Q20" s="4" t="n"/>
-      <c r="R20" s="4" t="n"/>
-      <c r="S20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1247,13 +1072,6 @@
       <c r="J21" s="4" t="n"/>
       <c r="K21" s="4" t="n"/>
       <c r="L21" s="4" t="n"/>
-      <c r="M21" s="4" t="n"/>
-      <c r="N21" s="4" t="n"/>
-      <c r="O21" s="4" t="n"/>
-      <c r="P21" s="4" t="n"/>
-      <c r="Q21" s="4" t="n"/>
-      <c r="R21" s="4" t="n"/>
-      <c r="S21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1265,11 +1083,7 @@
         </is>
       </c>
       <c r="C22" s="4" t="n"/>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
+      <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
       <c r="G22" s="4" t="n"/>
@@ -1278,13 +1092,6 @@
       <c r="J22" s="4" t="n"/>
       <c r="K22" s="4" t="n"/>
       <c r="L22" s="4" t="n"/>
-      <c r="M22" s="4" t="n"/>
-      <c r="N22" s="4" t="n"/>
-      <c r="O22" s="4" t="n"/>
-      <c r="P22" s="4" t="n"/>
-      <c r="Q22" s="4" t="n"/>
-      <c r="R22" s="4" t="n"/>
-      <c r="S22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1295,12 +1102,12 @@
           <t>Амир</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>игры</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="4" t="n"/>
       <c r="G23" s="4" t="n"/>
@@ -1309,13 +1116,6 @@
       <c r="J23" s="4" t="n"/>
       <c r="K23" s="4" t="n"/>
       <c r="L23" s="4" t="n"/>
-      <c r="M23" s="4" t="n"/>
-      <c r="N23" s="4" t="n"/>
-      <c r="O23" s="4" t="n"/>
-      <c r="P23" s="4" t="n"/>
-      <c r="Q23" s="4" t="n"/>
-      <c r="R23" s="4" t="n"/>
-      <c r="S23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1326,13 +1126,17 @@
           <t>Вика</t>
         </is>
       </c>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="n"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>танцы</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>все</t>
+        </is>
+      </c>
       <c r="F24" s="4" t="n"/>
       <c r="G24" s="4" t="n"/>
       <c r="H24" s="4" t="n"/>
@@ -1340,13 +1144,6 @@
       <c r="J24" s="4" t="n"/>
       <c r="K24" s="4" t="n"/>
       <c r="L24" s="4" t="n"/>
-      <c r="M24" s="4" t="n"/>
-      <c r="N24" s="4" t="n"/>
-      <c r="O24" s="4" t="n"/>
-      <c r="P24" s="4" t="n"/>
-      <c r="Q24" s="4" t="n"/>
-      <c r="R24" s="4" t="n"/>
-      <c r="S24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1357,12 +1154,12 @@
           <t>Даниил</t>
         </is>
       </c>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Изучать немецкий и Хойка</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n"/>
       <c r="G25" s="4" t="n"/>
@@ -1371,13 +1168,6 @@
       <c r="J25" s="4" t="n"/>
       <c r="K25" s="4" t="n"/>
       <c r="L25" s="4" t="n"/>
-      <c r="M25" s="4" t="n"/>
-      <c r="N25" s="4" t="n"/>
-      <c r="O25" s="4" t="n"/>
-      <c r="P25" s="4" t="n"/>
-      <c r="Q25" s="4" t="n"/>
-      <c r="R25" s="4" t="n"/>
-      <c r="S25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1398,13 +1188,6 @@
       <c r="J26" s="4" t="n"/>
       <c r="K26" s="4" t="n"/>
       <c r="L26" s="4" t="n"/>
-      <c r="M26" s="4" t="n"/>
-      <c r="N26" s="4" t="n"/>
-      <c r="O26" s="4" t="n"/>
-      <c r="P26" s="4" t="n"/>
-      <c r="Q26" s="4" t="n"/>
-      <c r="R26" s="4" t="n"/>
-      <c r="S26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1416,12 +1199,12 @@
         </is>
       </c>
       <c r="C27" s="4" t="n"/>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>✓ есть</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Некомпетентность</t>
+        </is>
+      </c>
       <c r="F27" s="4" t="n"/>
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="4" t="n"/>
@@ -1429,26 +1212,13 @@
       <c r="J27" s="4" t="n"/>
       <c r="K27" s="4" t="n"/>
       <c r="L27" s="4" t="n"/>
-      <c r="M27" s="4" t="n"/>
-      <c r="N27" s="4" t="n"/>
-      <c r="O27" s="4" t="n"/>
-      <c r="P27" s="4" t="n"/>
-      <c r="Q27" s="4" t="n"/>
-      <c r="R27" s="4" t="n"/>
-      <c r="S27" s="4" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation sqref="F2:F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"общага,дом"</formula1>
-    </dataValidation>
-    <dataValidation sqref="N2:N27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"первый ряд,середина,сзади,у окна,где придётся"</formula1>
-    </dataValidation>
-    <dataValidation sqref="O2:O27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="H2:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"сам подходит,надо подойти самому,игнорит сначала"</formula1>
     </dataValidation>
-    <dataValidation sqref="R2:R27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"да,нет,только дружба"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1462,7 +1232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Z27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1482,9 +1252,18 @@
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="48" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>№</t>
@@ -1568,6 +1347,51 @@
       <c r="Q1" s="5" t="inlineStr">
         <is>
           <t>Заметки</t>
+        </is>
+      </c>
+      <c r="R1" s="5" t="inlineStr">
+        <is>
+          <t>Харизма (0–10)</t>
+        </is>
+      </c>
+      <c r="S1" s="5" t="inlineStr">
+        <is>
+          <t>Живёт</t>
+        </is>
+      </c>
+      <c r="T1" s="5" t="inlineStr">
+        <is>
+          <t>Почему на мехмат</t>
+        </is>
+      </c>
+      <c r="U1" s="5" t="inlineStr">
+        <is>
+          <t>Хобби</t>
+        </is>
+      </c>
+      <c r="V1" s="5" t="inlineStr">
+        <is>
+          <t>О чём говорить</t>
+        </is>
+      </c>
+      <c r="W1" s="5" t="inlineStr">
+        <is>
+          <t>Бесит</t>
+        </is>
+      </c>
+      <c r="X1" s="5" t="inlineStr">
+        <is>
+          <t>Фишка</t>
+        </is>
+      </c>
+      <c r="Y1" s="5" t="inlineStr">
+        <is>
+          <t>Где сидит</t>
+        </is>
+      </c>
+      <c r="Z1" s="5" t="inlineStr">
+        <is>
+          <t>Как знакомится</t>
         </is>
       </c>
     </row>
@@ -1653,6 +1477,37 @@
           <t>старше всех, уже училась на мехмате; преподы не любят за пропуски</t>
         </is>
       </c>
+      <c r="R2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>общага</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>Браво Старс</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="n"/>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>Препод Габу</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="n"/>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>первый ряд</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>сам подходит</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -1724,6 +1579,29 @@
       </c>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>дом</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="n"/>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>Липсинги</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="n"/>
+      <c r="W3" s="2" t="n"/>
+      <c r="X3" s="2" t="n"/>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>где придётся</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -1795,6 +1673,31 @@
           <t>ровесник Адины</t>
         </is>
       </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>высокая</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>общага</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="n"/>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>Игры в том числе бравл старс</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="n"/>
+      <c r="W4" s="2" t="n"/>
+      <c r="X4" s="2" t="n"/>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>первый ряд</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -1862,6 +1765,33 @@
       </c>
       <c r="P5" s="2" t="n"/>
       <c r="Q5" s="2" t="n"/>
+      <c r="R5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>дом</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="n"/>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>Собирал свою машинку</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Машинах</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="n"/>
+      <c r="X5" s="2" t="n"/>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>где придётся</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1929,6 +1859,29 @@
           <t>играет на инструментах</t>
         </is>
       </c>
+      <c r="R6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>дом</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="n"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>Творчество</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="n"/>
+      <c r="W6" s="2" t="n"/>
+      <c r="X6" s="2" t="n"/>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>где придётся</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -2000,6 +1953,29 @@
           <t>только универ и дом; разговор не поддержит</t>
         </is>
       </c>
+      <c r="R7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>дом</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>загадка</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n"/>
+      <c r="V7" s="2" t="n"/>
+      <c r="W7" s="2" t="n"/>
+      <c r="X7" s="2" t="n"/>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>середина</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -2067,6 +2043,29 @@
           <t>чёрный юмор про смерть — просто манера шутить</t>
         </is>
       </c>
+      <c r="R8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>дом</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="n"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>Игры и одежда и Музка</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="n"/>
+      <c r="W8" s="2" t="n"/>
+      <c r="X8" s="2" t="n"/>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>первый ряд</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -2134,6 +2133,33 @@
           <t>гум. школа, на год старше, играет в комп</t>
         </is>
       </c>
+      <c r="R9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>дом</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>Хотел на мехмат</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>Игры, Саморазвитие</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="n"/>
+      <c r="W9" s="2" t="n"/>
+      <c r="X9" s="2" t="n"/>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>сзади</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -2193,6 +2219,29 @@
       </c>
       <c r="P10" s="2" t="n"/>
       <c r="Q10" s="2" t="n"/>
+      <c r="R10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>общага</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="n"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>Танцы</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="n"/>
+      <c r="W10" s="2" t="n"/>
+      <c r="X10" s="2" t="n"/>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>середина</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -2248,6 +2297,25 @@
       </c>
       <c r="P11" s="2" t="n"/>
       <c r="Q11" s="2" t="n"/>
+      <c r="R11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>общага</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="n"/>
+      <c r="U11" s="2" t="n"/>
+      <c r="V11" s="2" t="n"/>
+      <c r="W11" s="2" t="n"/>
+      <c r="X11" s="2" t="n"/>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>середина</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -2307,6 +2375,25 @@
           <t>«всё может сдать»</t>
         </is>
       </c>
+      <c r="R12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>дом</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="n"/>
+      <c r="U12" s="2" t="n"/>
+      <c r="V12" s="2" t="n"/>
+      <c r="W12" s="2" t="n"/>
+      <c r="X12" s="2" t="n"/>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>где придётся</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -2370,6 +2457,37 @@
           <t>редко с кем общается</t>
         </is>
       </c>
+      <c r="R13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>дом</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>Поприколу</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>Музыка игры фильмы</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="n"/>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>Касания</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="n"/>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>сзади</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -2429,6 +2547,25 @@
       </c>
       <c r="P14" s="2" t="n"/>
       <c r="Q14" s="2" t="n"/>
+      <c r="R14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>дом</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="n"/>
+      <c r="U14" s="2" t="n"/>
+      <c r="V14" s="2" t="n"/>
+      <c r="W14" s="2" t="n"/>
+      <c r="X14" s="2" t="n"/>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>сзади</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -2488,6 +2625,25 @@
           <t>в школе была отличницей, здесь тяжело</t>
         </is>
       </c>
+      <c r="R15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>дом</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="n"/>
+      <c r="U15" s="2" t="n"/>
+      <c r="V15" s="2" t="n"/>
+      <c r="W15" s="2" t="n"/>
+      <c r="X15" s="2" t="n"/>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>первый ряд</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -2555,6 +2711,29 @@
           <t>за ней ходят мальчики</t>
         </is>
       </c>
+      <c r="R16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>дом</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="n"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>Липсинги</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="n"/>
+      <c r="W16" s="2" t="n"/>
+      <c r="X16" s="2" t="n"/>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>где придётся</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -2622,6 +2801,37 @@
         </is>
       </c>
       <c r="Q17" s="2" t="n"/>
+      <c r="R17" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>дом</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>Хочет заниматься астрофизикой</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>Свой телеграм канал. И тик токи липсинги</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="n"/>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>Шутки про женщин и лгбт</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="n"/>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>у окна</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -2681,6 +2891,37 @@
       </c>
       <c r="P18" s="2" t="n"/>
       <c r="Q18" s="2" t="n"/>
+      <c r="R18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>общага</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>Хотел</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>Кодить фильмы</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="n"/>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>вика</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="n"/>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>где придётся</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -2740,6 +2981,33 @@
       </c>
       <c r="P19" s="2" t="n"/>
       <c r="Q19" s="2" t="n"/>
+      <c r="R19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>дом</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>Хотел год подождать</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>Загадка</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="n"/>
+      <c r="W19" s="2" t="n"/>
+      <c r="X19" s="2" t="n"/>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>сзади</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -2799,6 +3067,41 @@
           <t>физмат-школа</t>
         </is>
       </c>
+      <c r="R20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>дом</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>хотел</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>Кодинг и игры</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="n"/>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>Касания</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>Моргать</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>сзади</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -2854,6 +3157,25 @@
       </c>
       <c r="P21" s="2" t="n"/>
       <c r="Q21" s="2" t="n"/>
+      <c r="R21" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>дом</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="n"/>
+      <c r="U21" s="2" t="n"/>
+      <c r="V21" s="2" t="n"/>
+      <c r="W21" s="2" t="n"/>
+      <c r="X21" s="2" t="n"/>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>у окна</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -2917,6 +3239,25 @@
           <t>работает репетитором</t>
         </is>
       </c>
+      <c r="R22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>дом</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="n"/>
+      <c r="U22" s="2" t="n"/>
+      <c r="V22" s="2" t="n"/>
+      <c r="W22" s="2" t="n"/>
+      <c r="X22" s="2" t="n"/>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>где придётся</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -2980,6 +3321,33 @@
           <t>собирается в Тайвань</t>
         </is>
       </c>
+      <c r="R23" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>дом</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>Скипнуть год и поступить в тайвань</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>игры</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="n"/>
+      <c r="W23" s="2" t="n"/>
+      <c r="X23" s="2" t="n"/>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>у окна</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -3039,6 +3407,33 @@
       </c>
       <c r="P24" s="2" t="n"/>
       <c r="Q24" s="2" t="n"/>
+      <c r="R24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>общага</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="n"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>танцы</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="n"/>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>все</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="n"/>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>где придётся</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -3102,6 +3497,29 @@
           <t>гум. школа, учёбу не потянет</t>
         </is>
       </c>
+      <c r="R25" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>дом</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="n"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>Изучать немецкий и Хойка</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="n"/>
+      <c r="W25" s="2" t="n"/>
+      <c r="X25" s="2" t="n"/>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>середина</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -3161,6 +3579,25 @@
           <t>всё списывает</t>
         </is>
       </c>
+      <c r="R26" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>общага</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="n"/>
+      <c r="U26" s="2" t="n"/>
+      <c r="V26" s="2" t="n"/>
+      <c r="W26" s="2" t="n"/>
+      <c r="X26" s="2" t="n"/>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>середина</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -3224,6 +3661,29 @@
           <t>общается с преподами</t>
         </is>
       </c>
+      <c r="R27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>дом</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="n"/>
+      <c r="U27" s="2" t="n"/>
+      <c r="V27" s="2" t="n"/>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>Некомпетентность</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="n"/>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>первый ряд</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3236,7 +3696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -3266,18 +3726,10 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Даниил: шутки про Германию намекают на настоящее имя. Оставить или другая фишка?</t>
+          <t>Полные линии: у кого ещё, кроме Адины? Всего 5–7 человек.</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Полные линии: у кого ещё, кроме Адины? Всего 5–7 человек.</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/game/design/characters/odnogruppniki.xlsx
+++ b/game/design/characters/odnogruppniki.xlsx
@@ -108,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -135,6 +135,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -502,21 +505,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="48" customHeight="1">
@@ -532,50 +529,20 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Хобби, чем увлекается</t>
+          <t>Привычка, фишка</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>О чём с ним интересно говорить</t>
+          <t>Как знакомится с героем</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Что бесит / о чём лучше не говорить</t>
+          <t>Может быть любовь с героем? (не с теми, кто точно вылетит)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Чего хочет в этом семестре</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Привычка, фишка</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Как знакомится с героем</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Как относится к преподам</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>С кем обычно на перерыве</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Может быть любовь с героем?</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Реальный случай (для ивента)</t>
         </is>
@@ -590,28 +557,18 @@
           <t>Адина</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Браво Старс</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Препод Габу</t>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>сам подходит</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>только дружба</t>
         </is>
       </c>
       <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>сам подходит</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" s="4" t="n"/>
-      <c r="K2" s="4" t="n"/>
-      <c r="L2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -622,20 +579,14 @@
           <t>Сайгуль</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Липсинги</t>
-        </is>
-      </c>
+      <c r="C3" s="4" t="n"/>
       <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
       <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
-      <c r="J3" s="4" t="n"/>
-      <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -646,20 +597,10 @@
           <t>Ноидор</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Игры в том числе бравл старс</t>
-        </is>
-      </c>
+      <c r="C4" s="4" t="n"/>
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
-      <c r="J4" s="4" t="n"/>
-      <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -670,24 +611,10 @@
           <t>Кирлан</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Собирал свою машинку</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Машинах</t>
-        </is>
-      </c>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -698,20 +625,10 @@
           <t>Бауржан</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Творчество</t>
-        </is>
-      </c>
+      <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -724,14 +641,12 @@
       </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
       <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -742,20 +657,10 @@
           <t>Мирис</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Игры и одежда и Музка</t>
-        </is>
-      </c>
+      <c r="C8" s="4" t="n"/>
       <c r="D8" s="4" t="n"/>
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -766,20 +671,14 @@
           <t>Аланас</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Игры, Саморазвитие</t>
-        </is>
-      </c>
+      <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -790,20 +689,10 @@
           <t>Азиза</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Танцы</t>
-        </is>
-      </c>
+      <c r="C10" s="4" t="n"/>
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="n"/>
-      <c r="L10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -818,12 +707,6 @@
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
-      <c r="L11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -838,12 +721,6 @@
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -854,24 +731,14 @@
           <t>Исан</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Музыка игры фильмы</t>
-        </is>
-      </c>
+      <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Касания</t>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>только дружба</t>
         </is>
       </c>
       <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -886,12 +753,6 @@
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -904,14 +765,12 @@
       </c>
       <c r="C15" s="4" t="n"/>
       <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
       <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="n"/>
-      <c r="L15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -922,20 +781,10 @@
           <t>Даша</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Липсинги</t>
-        </is>
-      </c>
+      <c r="C16" s="4" t="n"/>
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4" t="n"/>
-      <c r="L16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -946,28 +795,14 @@
           <t>Адалина</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Свой телеграм канал. И тик токи липсинги</t>
-        </is>
-      </c>
+      <c r="C17" s="4" t="n"/>
       <c r="D17" s="4" t="n"/>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Шутки про женщин и лгбт</t>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>да</t>
         </is>
       </c>
       <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="n"/>
-      <c r="J17" s="4" t="n"/>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>только дружба</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -978,24 +813,18 @@
           <t>Сендир</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Кодить фильмы</t>
-        </is>
-      </c>
+      <c r="C18" s="4" t="n"/>
       <c r="D18" s="4" t="n"/>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>вика</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
-      <c r="J18" s="4" t="n"/>
-      <c r="K18" s="4" t="n"/>
-      <c r="L18" s="4" t="n"/>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>только дружба</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>Эспандер (напиши распишу)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1006,20 +835,14 @@
           <t>Алнар</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Загадка</t>
-        </is>
-      </c>
+      <c r="C19" s="4" t="n"/>
       <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
       <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="n"/>
-      <c r="K19" s="4" t="n"/>
-      <c r="L19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1030,28 +853,22 @@
           <t>Саид</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Кодинг и игры</t>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Моргать</t>
         </is>
       </c>
       <c r="D20" s="4" t="n"/>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Касания</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Моргать</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n"/>
-      <c r="K20" s="4" t="n"/>
-      <c r="L20" s="4" t="n"/>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>только дружба</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>Олимпиада филиальская, пицца с алгебраистом</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1066,12 +883,6 @@
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
-      <c r="J21" s="4" t="n"/>
-      <c r="K21" s="4" t="n"/>
-      <c r="L21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1084,14 +895,12 @@
       </c>
       <c r="C22" s="4" t="n"/>
       <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
       <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
-      <c r="J22" s="4" t="n"/>
-      <c r="K22" s="4" t="n"/>
-      <c r="L22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1102,20 +911,14 @@
           <t>Амир</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>игры</t>
-        </is>
-      </c>
+      <c r="C23" s="4" t="n"/>
       <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>только дружба</t>
+        </is>
+      </c>
       <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
-      <c r="J23" s="4" t="n"/>
-      <c r="K23" s="4" t="n"/>
-      <c r="L23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1126,24 +929,10 @@
           <t>Вика</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>танцы</t>
-        </is>
-      </c>
+      <c r="C24" s="4" t="n"/>
       <c r="D24" s="4" t="n"/>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>все</t>
-        </is>
-      </c>
+      <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="4" t="n"/>
-      <c r="K24" s="4" t="n"/>
-      <c r="L24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1154,20 +943,10 @@
           <t>Даниил</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Изучать немецкий и Хойка</t>
-        </is>
-      </c>
+      <c r="C25" s="4" t="n"/>
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n"/>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n"/>
-      <c r="J25" s="4" t="n"/>
-      <c r="K25" s="4" t="n"/>
-      <c r="L25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1182,12 +961,6 @@
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="4" t="n"/>
-      <c r="K26" s="4" t="n"/>
-      <c r="L26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1200,25 +973,15 @@
       </c>
       <c r="C27" s="4" t="n"/>
       <c r="D27" s="4" t="n"/>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>Некомпетентность</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
-      <c r="J27" s="4" t="n"/>
-      <c r="K27" s="4" t="n"/>
-      <c r="L27" s="4" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="H2:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"сам подходит,надо подойти самому,игнорит сначала"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"да,нет,только дружба"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1232,7 +995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z27"/>
+  <dimension ref="A1:AD27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1261,6 +1024,10 @@
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="18" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="22" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1" ht="48" customHeight="1">
@@ -1394,6 +1161,26 @@
           <t>Как знакомится</t>
         </is>
       </c>
+      <c r="AA1" s="5" t="inlineStr">
+        <is>
+          <t>Темы для разговора</t>
+        </is>
+      </c>
+      <c r="AB1" s="5" t="inlineStr">
+        <is>
+          <t>К преподам</t>
+        </is>
+      </c>
+      <c r="AC1" s="5" t="inlineStr">
+        <is>
+          <t>Любовь с героем</t>
+        </is>
+      </c>
+      <c r="AD1" s="5" t="inlineStr">
+        <is>
+          <t>Реальный случай</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -1508,6 +1295,18 @@
           <t>сам подходит</t>
         </is>
       </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>браво старс, учёба</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="n"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>только дружба</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -1602,6 +1401,18 @@
         </is>
       </c>
       <c r="Z3" s="2" t="n"/>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>липсинги, учёба</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="n"/>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -1698,6 +1509,14 @@
         </is>
       </c>
       <c r="Z4" s="2" t="n"/>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>игры в том числе бравл старс, учёба</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="n"/>
+      <c r="AC4" s="2" t="n"/>
+      <c r="AD4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -1792,6 +1611,14 @@
         </is>
       </c>
       <c r="Z5" s="2" t="n"/>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>машинах, учёба</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="n"/>
+      <c r="AC5" s="2" t="n"/>
+      <c r="AD5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1882,6 +1709,14 @@
         </is>
       </c>
       <c r="Z6" s="2" t="n"/>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>творчество, учёба</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="n"/>
+      <c r="AC6" s="2" t="n"/>
+      <c r="AD6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1976,6 +1811,18 @@
         </is>
       </c>
       <c r="Z7" s="2" t="n"/>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>учёба</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="n"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -2066,6 +1913,14 @@
         </is>
       </c>
       <c r="Z8" s="2" t="n"/>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>игры и одежда и музка, учёба</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="n"/>
+      <c r="AC8" s="2" t="n"/>
+      <c r="AD8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -2160,6 +2015,18 @@
         </is>
       </c>
       <c r="Z9" s="2" t="n"/>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>игры, саморазвитие, учёба</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="n"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="AD9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -2242,6 +2109,14 @@
         </is>
       </c>
       <c r="Z10" s="2" t="n"/>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>танцы, учёба</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="n"/>
+      <c r="AC10" s="2" t="n"/>
+      <c r="AD10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -2316,6 +2191,14 @@
         </is>
       </c>
       <c r="Z11" s="2" t="n"/>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>учёба</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="n"/>
+      <c r="AC11" s="2" t="n"/>
+      <c r="AD11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -2394,6 +2277,14 @@
         </is>
       </c>
       <c r="Z12" s="2" t="n"/>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>учёба</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="n"/>
+      <c r="AC12" s="2" t="n"/>
+      <c r="AD12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -2488,6 +2379,18 @@
         </is>
       </c>
       <c r="Z13" s="2" t="n"/>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>музыка игры фильмы, учёба</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="n"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>только дружба</t>
+        </is>
+      </c>
+      <c r="AD13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -2566,6 +2469,14 @@
         </is>
       </c>
       <c r="Z14" s="2" t="n"/>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>учёба</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="n"/>
+      <c r="AC14" s="2" t="n"/>
+      <c r="AD14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -2644,6 +2555,18 @@
         </is>
       </c>
       <c r="Z15" s="2" t="n"/>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>учёба</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="n"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="AD15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -2734,6 +2657,14 @@
         </is>
       </c>
       <c r="Z16" s="2" t="n"/>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>липсинги, учёба</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="n"/>
+      <c r="AC16" s="2" t="n"/>
+      <c r="AD16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -2832,6 +2763,18 @@
         </is>
       </c>
       <c r="Z17" s="2" t="n"/>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>свой телеграм канал. и тик токи липсинги, учёба</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="n"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="AD17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -2922,6 +2865,26 @@
         </is>
       </c>
       <c r="Z18" s="2" t="n"/>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>кодить фильмы, учёба</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>Хорошо</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>только дружба</t>
+        </is>
+      </c>
+      <c r="AD18" s="2" t="inlineStr">
+        <is>
+          <t>Эспандер (напиши распишу)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -3008,6 +2971,18 @@
         </is>
       </c>
       <c r="Z19" s="2" t="n"/>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>учёба</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="n"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="AD19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -3102,6 +3077,26 @@
         </is>
       </c>
       <c r="Z20" s="2" t="n"/>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>кодинг и игры, учёба</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>Отлично</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>только дружба</t>
+        </is>
+      </c>
+      <c r="AD20" s="2" t="inlineStr">
+        <is>
+          <t>Олимпиада филиальская, пицца с алгебраистом</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -3176,6 +3171,14 @@
         </is>
       </c>
       <c r="Z21" s="2" t="n"/>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>учёба</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="n"/>
+      <c r="AC21" s="2" t="n"/>
+      <c r="AD21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -3258,6 +3261,18 @@
         </is>
       </c>
       <c r="Z22" s="2" t="n"/>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>учёба</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="n"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="AD22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -3348,6 +3363,18 @@
         </is>
       </c>
       <c r="Z23" s="2" t="n"/>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>игры, учёба</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="n"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>только дружба</t>
+        </is>
+      </c>
+      <c r="AD23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -3434,6 +3461,14 @@
         </is>
       </c>
       <c r="Z24" s="2" t="n"/>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>танцы, учёба</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="n"/>
+      <c r="AC24" s="2" t="n"/>
+      <c r="AD24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -3520,6 +3555,14 @@
         </is>
       </c>
       <c r="Z25" s="2" t="n"/>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>изучать немецкий и хойка, учёба</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="n"/>
+      <c r="AC25" s="2" t="n"/>
+      <c r="AD25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -3598,6 +3641,14 @@
         </is>
       </c>
       <c r="Z26" s="2" t="n"/>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>учёба</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="n"/>
+      <c r="AC26" s="2" t="n"/>
+      <c r="AD26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -3684,6 +3735,14 @@
         </is>
       </c>
       <c r="Z27" s="2" t="n"/>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>учёба</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="n"/>
+      <c r="AC27" s="2" t="n"/>
+      <c r="AD27" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
